--- a/diseases/d126/2015-2019.xlsx
+++ b/diseases/d126/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1798,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2683,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3568,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4465,9 +4453,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5486,6 @@
       <c r="O34" t="n">
         <v>5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.009807015297364935</v>
       </c>
@@ -6389,9 +6371,6 @@
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.009807015297364935</v>
       </c>
@@ -7277,9 +7256,6 @@
       <c r="O46" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.007845612237891948</v>
       </c>
@@ -8313,9 +8289,6 @@
       <c r="O53" t="n">
         <v>17</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03334385201104077</v>
       </c>
@@ -9201,9 +9174,6 @@
       <c r="O59" t="n">
         <v>5</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.009807015297364935</v>
       </c>
@@ -10237,9 +10207,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.001961403059472987</v>
       </c>
@@ -11125,9 +11092,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11977,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12122,6 @@
       <c r="O79" t="n">
         <v>3</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -13297,9 +13255,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -13445,9 +13400,6 @@
       <c r="O87" t="n">
         <v>2</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.02015462629291927</v>
       </c>
@@ -14581,9 +14533,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -14729,9 +14678,6 @@
       <c r="O95" t="n">
         <v>3</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -15717,9 +15663,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -15865,9 +15808,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -17001,9 +16941,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17149,9 +17086,6 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -18285,9 +18219,6 @@
       <c r="O117" t="n">
         <v>2</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -18433,9 +18364,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -19569,9 +19497,6 @@
       <c r="O125" t="n">
         <v>5</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.009746999283926951</v>
       </c>
@@ -19717,9 +19642,6 @@
       <c r="O126" t="n">
         <v>5</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.05038656573229819</v>
       </c>
@@ -21001,9 +20923,6 @@
       <c r="O134" t="n">
         <v>20</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0389879971357078</v>
       </c>
@@ -21149,9 +21068,6 @@
       <c r="O135" t="n">
         <v>7</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.07054119202521747</v>
       </c>
@@ -22285,9 +22201,6 @@
       <c r="O142" t="n">
         <v>17</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.03313979756535163</v>
       </c>
@@ -22433,9 +22346,6 @@
       <c r="O143" t="n">
         <v>8</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.0806185051716771</v>
       </c>
@@ -23569,9 +23479,6 @@
       <c r="O150" t="n">
         <v>9</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01754459871106851</v>
       </c>
@@ -23717,9 +23624,6 @@
       <c r="O151" t="n">
         <v>6</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -25001,9 +24905,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -25149,9 +25050,6 @@
       <c r="O160" t="n">
         <v>5</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.05038656573229819</v>
       </c>
@@ -26285,9 +26183,6 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -26433,9 +26328,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -27717,9 +27609,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -27865,9 +27754,6 @@
       <c r="O177" t="n">
         <v>5</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.04971235684643301</v>
       </c>
@@ -28409,9 +28295,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -28557,9 +28440,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -29101,9 +28981,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -29249,9 +29126,6 @@
       <c r="O185" t="n">
         <v>2</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -29793,9 +29667,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -29941,9 +29812,6 @@
       <c r="O189" t="n">
         <v>1</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.009942471369286603</v>
       </c>
@@ -30485,9 +30353,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -30633,9 +30498,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.009942471369286603</v>
       </c>
@@ -31177,9 +31039,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -31325,9 +31184,6 @@
       <c r="O197" t="n">
         <v>2</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -31869,9 +31725,6 @@
       <c r="O200" t="n">
         <v>2</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -32017,9 +31870,6 @@
       <c r="O201" t="n">
         <v>3</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.02982741410785981</v>
       </c>
@@ -32561,9 +32411,6 @@
       <c r="O204" t="n">
         <v>13</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.02524944975379407</v>
       </c>
@@ -32709,9 +32556,6 @@
       <c r="O205" t="n">
         <v>13</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.1292521278007258</v>
       </c>
@@ -33253,9 +33097,6 @@
       <c r="O208" t="n">
         <v>19</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.03690304194785287</v>
       </c>
@@ -33401,9 +33242,6 @@
       <c r="O209" t="n">
         <v>7</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.06959729958500621</v>
       </c>
@@ -33945,9 +33783,6 @@
       <c r="O212" t="n">
         <v>9</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.0174803882910882</v>
       </c>
@@ -34093,9 +33928,6 @@
       <c r="O213" t="n">
         <v>5</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.04971235684643301</v>
       </c>
@@ -34637,9 +34469,6 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -34785,9 +34614,6 @@
       <c r="O217" t="n">
         <v>5</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.04971235684643301</v>
       </c>
@@ -35329,9 +35155,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -35477,9 +35300,6 @@
       <c r="O221" t="n">
         <v>2</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -36021,9 +35841,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -36169,9 +35986,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -36713,9 +36527,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -36861,9 +36672,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -37405,9 +37213,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -37553,9 +37358,6 @@
       <c r="O233" t="n">
         <v>2</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.0196552382757855</v>
       </c>
@@ -38097,9 +37899,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -38245,9 +38044,6 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.009827619137892749</v>
       </c>
@@ -38789,9 +38585,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -38937,9 +38730,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -39481,9 +39271,6 @@
       <c r="O244" t="n">
         <v>2</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.00387289964422382</v>
       </c>
@@ -39629,9 +39416,6 @@
       <c r="O245" t="n">
         <v>8</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.07862095310314199</v>
       </c>
@@ -40173,9 +39957,6 @@
       <c r="O248" t="n">
         <v>7</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.01355514875478337</v>
       </c>
@@ -40321,9 +40102,6 @@
       <c r="O249" t="n">
         <v>33</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.3243114315504607</v>
       </c>
@@ -40865,9 +40643,6 @@
       <c r="O252" t="n">
         <v>16</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.03098319715379056</v>
       </c>
@@ -41013,9 +40788,6 @@
       <c r="O253" t="n">
         <v>78</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.7665542927556344</v>
       </c>
@@ -41557,9 +41329,6 @@
       <c r="O256" t="n">
         <v>10</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.0193644982211191</v>
       </c>
@@ -41705,9 +41474,6 @@
       <c r="O257" t="n">
         <v>23</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.2260352401715333</v>
       </c>
@@ -42249,9 +42015,6 @@
       <c r="O260" t="n">
         <v>11</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.02130094804323101</v>
       </c>
@@ -42397,9 +42160,6 @@
       <c r="O261" t="n">
         <v>15</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.1474142870683912</v>
       </c>
@@ -42941,9 +42701,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -43089,9 +42846,6 @@
       <c r="O265" t="n">
         <v>14</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.1375866679304985</v>
       </c>
@@ -43633,9 +43387,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -43781,9 +43532,6 @@
       <c r="O269" t="n">
         <v>4</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.03931047655157099</v>
       </c>
@@ -44325,9 +44073,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -44473,9 +44218,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -44869,9 +44611,6 @@
       <c r="O275" t="n">
         <v>3</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.0291853635401846</v>
       </c>
@@ -45413,9 +45152,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -45561,9 +45297,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -45957,9 +45690,6 @@
       <c r="O281" t="n">
         <v>6</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.0583707270803692</v>
       </c>
@@ -46501,9 +46231,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -46649,9 +46376,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -47045,9 +46769,6 @@
       <c r="O287" t="n">
         <v>5</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.04864227256697433</v>
       </c>
@@ -47589,9 +47310,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -47737,9 +47455,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -48133,9 +47848,6 @@
       <c r="O293" t="n">
         <v>2</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.01945690902678973</v>
       </c>
@@ -48677,9 +48389,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -48825,9 +48534,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -49221,9 +48927,6 @@
       <c r="O299" t="n">
         <v>5</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.04864227256697433</v>
       </c>
@@ -49765,9 +49468,6 @@
       <c r="O302" t="n">
         <v>1</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -49913,9 +49613,6 @@
       <c r="O303" t="n">
         <v>1</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -50309,9 +50006,6 @@
       <c r="O305" t="n">
         <v>2</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.01945690902678973</v>
       </c>
@@ -50853,9 +50547,6 @@
       <c r="O308" t="n">
         <v>2</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.003863402004402502</v>
       </c>
@@ -51001,9 +50692,6 @@
       <c r="O309" t="n">
         <v>15</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.280492818402124</v>
       </c>
@@ -51397,9 +51085,6 @@
       <c r="O311" t="n">
         <v>7</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.06809918159376406</v>
       </c>
@@ -51941,9 +51626,6 @@
       <c r="O314" t="n">
         <v>14</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.02704381403081751</v>
       </c>
@@ -52089,9 +51771,6 @@
       <c r="O315" t="n">
         <v>15</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.280492818402124</v>
       </c>
@@ -52485,9 +52164,6 @@
       <c r="O317" t="n">
         <v>26</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0.2529398173482665</v>
       </c>
@@ -53029,9 +52705,6 @@
       <c r="O320" t="n">
         <v>14</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.02704381403081751</v>
       </c>
@@ -53177,9 +52850,6 @@
       <c r="O321" t="n">
         <v>6</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.1121971273608496</v>
       </c>
@@ -53573,9 +53243,6 @@
       <c r="O323" t="n">
         <v>16</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.1556552722143179</v>
       </c>
@@ -54117,9 +53784,6 @@
       <c r="O326" t="n">
         <v>5</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.009658505011006253</v>
       </c>
@@ -54265,9 +53929,6 @@
       <c r="O327" t="n">
         <v>5</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.09349760613404134</v>
       </c>
@@ -54661,9 +54322,6 @@
       <c r="O329" t="n">
         <v>9</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.08755609062055379</v>
       </c>
@@ -55205,9 +54863,6 @@
       <c r="O332" t="n">
         <v>6</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0.0115902060132075</v>
       </c>
@@ -55353,9 +55008,6 @@
       <c r="O333" t="n">
         <v>6</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.1121971273608496</v>
       </c>
@@ -55749,9 +55401,6 @@
       <c r="O335" t="n">
         <v>5</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0.04864227256697433</v>
       </c>
@@ -56293,9 +55942,6 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
@@ -56441,9 +56087,6 @@
       <c r="O339" t="n">
         <v>2</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.03739904245361654</v>
       </c>
@@ -56836,9 +56479,6 @@
       </c>
       <c r="O341" t="n">
         <v>4</v>
-      </c>
-      <c r="Q341" t="n">
-        <v>0</v>
       </c>
       <c r="R341" t="n">
         <v>0.03891381805357946</v>
